--- a/checklist_forms/018_van_safety_checklist--checklist_forms.xlsx
+++ b/checklist_forms/018_van_safety_checklist--checklist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>van_safety_checklist_form_1</t>
+          <t>van_safety_checklist_1_form</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Van Safety Checklist Form 1</t>
+          <t>What type of van do you have?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>van_safety_checklist_1_checklist_item_1</t>
+          <t>van_safety_checklist_1_frequency_of_use</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Van Safety Checklist Item 1</t>
+          <t>How often is the van driven?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>van_safety_checklist_1_checklist_item_2</t>
+          <t>van_safety_checklist_1_usage</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Van Safety Checklist Item 2</t>
+          <t>What is the van used for?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,35 +589,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>van_safety_checklist_1_checklist_item_3</t>
+          <t>van_safety_checklist_1_seatbelts</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Van Safety Checklist Item 3</t>
+          <t>Are all passengers wearing seatbelts while traveling in the van?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>van_safety_checklist_1_checklist_item_4</t>
+          <t>van_safety_checklist_1_maintenance</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Van Safety Checklist Item 4</t>
+          <t>Has the van undergone regular maintenance (oil changes, tire rotations, etc.)?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>van_safety_checklist_2_form_1</t>
+          <t>van_safety_checklist_1_driving_experience</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Van Safety Checklist Form 1</t>
+          <t>What is your driving experience with vans?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>van_safety_checklist_2_checklist_item_1</t>
+          <t>van_safety_checklist_1_passengers</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Van Safety Checklist Item 1</t>
+          <t>How many passengers can fit in the van comfortably?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>van_safety_checklist_2_checklist_item_2</t>
+          <t>van_safety_checklist_1_first_aid_kit</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Van Safety Checklist Item 2</t>
+          <t>Is the van equipped with a first aid kit?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>van_safety_checklist_2_checklist_item_3</t>
+          <t>van_safety_checklist_1_training</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Van Safety Checklist Item 3</t>
+          <t>Have you received training on van safety and usage?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>van_safety_checklist_2_checklist_item_4</t>
+          <t>van_safety_checklist_1_mileage</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Van Safety Checklist Item 4</t>
+          <t>What is your estimated annual mileage?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>van_safety_checklist_3_form_2</t>
+          <t>van_safety_checklist_1_emergency_exit</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Van Safety Checklist Form 2</t>
+          <t>Does the van have a functioning emergency exit?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>van_safety_checklist_3_checklist_item_1</t>
+          <t>van_safety_checklist_1_maintenance_schedule</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Van Safety Checklist Item 1</t>
+          <t>Do you follow recommended van maintenance schedules?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>van_safety_checklist_3_checklist_item_2</t>
+          <t>van_safety_checklist_2_form</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Van Safety Checklist Item 2</t>
+          <t>Van Safety Checklist Form 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>van_safety_checklist_3_checklist_item_3</t>
+          <t>van_safety_checklist_2_frequency_of_use</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Van Safety Checklist Item 3</t>
+          <t>How often is the van used for commuting?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>van_safety_checklist_4_form_3</t>
+          <t>van_safety_checklist_2_usage_type</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Van Safety Checklist Form 3</t>
+          <t>What is the van used for during commuting?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,23 +860,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>van_safety_checklist_4_checklist_item_1</t>
+          <t>van_safety_checklist_2_seatbelts_commute</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Van Safety Checklist Item 1</t>
+          <t>Are all passengers wearing seatbelts during commute?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>van_safety_checklist_4_checklist_item_2</t>
+          <t>van_safety_checklist_2_maintenance_commute</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Van Safety Checklist Item 2</t>
+          <t>Has the van undergone regular maintenance (oil changes, tire rotations, etc.) during commute?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,17 +906,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>van_safety_checklist_4_checklist_item_3</t>
+          <t>van_safety_checklist_2_emergency_exit_commute</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Van Safety Checklist Item 3</t>
+          <t>Does the van have a functioning emergency exit during commute?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,21 +929,412 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>van_safety_checklist_4_checklist_item_4</t>
+          <t>van_safety_checklist_2_driving_experience_commute</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Van Safety Checklist Item 4</t>
+          <t>What is your driving experience with vans during commute?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>select_multiple</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_2_mileage_commute</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>What is your estimated annual mileage during commute?</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_3_form</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Van Safety Checklist Form 3</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_3_frequency_of_use</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>How often is the van used for family transportation?</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>select_multiple</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_3_usage_type</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>What is the van used for during family transportation?</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_3_seatbelts_family</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Are all passengers wearing seatbelts during family transportation?</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_3_maintenance_family</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Has the van undergone regular maintenance (oil changes, tire rotations, etc.) during family transportation?</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_3_emergency_exit_family</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Does the van have a functioning emergency exit during family transportation?</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>select_multiple</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_3_driving_experience_family</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>What is your driving experience with vans during family transportation?</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>select_multiple</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_3_mileage_family</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>What is your estimated annual mileage during family transportation?</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_4_form</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Van Safety Checklist Form 4</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_4_frequency_of_use</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>How often is the van used for cargo transport?</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>select_multiple</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_4_usage_type</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>What is the van used for during cargo transport?</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_4_seatbelts_cargo</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Are all passengers wearing seatbelts during cargo transport?</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_4_maintenance_cargo</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Has the van undergone regular maintenance (oil changes, tire rotations, etc.) during cargo transport?</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_4_emergency_exit_cargo</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Does the van have a functioning emergency exit during cargo transport?</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>select_multiple</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_4_driving_experience_cargo</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>What is your driving experience with vans during cargo transport?</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>select_multiple</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_4_mileage_cargo</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>What is your estimated annual mileage during cargo transport?</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -960,12 +1351,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="49" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -988,408 +1379,1377 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>van_safety_checklist_1_checklist_item_1_choices</t>
+          <t>van_safety_checklist_1_frequency_of_use_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>van_safety_checklist_item_1</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Van Safety Checklist Item 1</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>van_safety_checklist_1_checklist_item_1_choices</t>
+          <t>van_safety_checklist_1_frequency_of_use_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>van_safety_checklist_item_2</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Van Safety Checklist Item 2</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>van_safety_checklist_1_checklist_item_1_choices</t>
+          <t>van_safety_checklist_1_frequency_of_use_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>van_safety_checklist_item_3</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Van Safety Checklist Item 3</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>van_safety_checklist_1_checklist_item_2_choices</t>
+          <t>van_safety_checklist_1_usage_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>van_safety_checklist_item_4</t>
+          <t>commuting_to_work</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Van Safety Checklist Item 4</t>
+          <t>Commuting to work</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>van_safety_checklist_1_checklist_item_2_choices</t>
+          <t>van_safety_checklist_1_usage_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>van_safety_checklist_item_5</t>
+          <t>family_transportation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Van Safety Checklist Item 5</t>
+          <t>Family transportation</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>van_safety_checklist_1_checklist_item_2_choices</t>
+          <t>van_safety_checklist_1_usage_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>van_safety_checklist_item_6</t>
+          <t>cargo_transport</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Van Safety Checklist Item 6</t>
+          <t>Cargo transport</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>van_safety_checklist_1_checklist_item_3_choices</t>
+          <t>van_safety_checklist_1_seatbelts_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>van_safety_checklist_1_checklist_item_3_choices</t>
+          <t>van_safety_checklist_1_seatbelts_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>van_safety_checklist_1_checklist_item_4_choices</t>
+          <t>van_safety_checklist_1_maintenance_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>van_safety_checklist_1_checklist_item_4_choices</t>
+          <t>van_safety_checklist_1_maintenance_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>van_safety_checklist_2_checklist_item_1_choices</t>
+          <t>van_safety_checklist_1_driving_experience_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>less_than_1_year</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Less than 1 year</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>van_safety_checklist_2_checklist_item_1_choices</t>
+          <t>van_safety_checklist_1_driving_experience_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>1-5_years</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>1-5 years</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>van_safety_checklist_2_checklist_item_2_choices</t>
+          <t>van_safety_checklist_1_driving_experience_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>more_than_5_years</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>More than 5 years</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>van_safety_checklist_2_checklist_item_2_choices</t>
+          <t>van_safety_checklist_1_passengers_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>less_than_5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Less than 5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>van_safety_checklist_3_checklist_item_1_choices</t>
+          <t>van_safety_checklist_1_passengers_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>5-10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>5-10</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>van_safety_checklist_3_checklist_item_1_choices</t>
+          <t>van_safety_checklist_1_passengers_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>more_than_10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>More than 10</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>van_safety_checklist_3_checklist_item_2_choices</t>
+          <t>van_safety_checklist_1_first_aid_kit_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>van_safety_checklist_3_checklist_item_2_choices</t>
+          <t>van_safety_checklist_1_first_aid_kit_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>van_safety_checklist_3_checklist_item_3_choices</t>
+          <t>van_safety_checklist_1_training_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>van_safety_checklist_3_checklist_item_3_choices</t>
+          <t>van_safety_checklist_1_training_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>van_safety_checklist_4_checklist_item_1_choices</t>
+          <t>van_safety_checklist_1_mileage_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>less_than_10,000_miles</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Less than 10,000 miles</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>van_safety_checklist_4_checklist_item_1_choices</t>
+          <t>van_safety_checklist_1_mileage_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>10,000-20,000_miles</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>10,000-20,000 miles</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>van_safety_checklist_4_checklist_item_2_choices</t>
+          <t>van_safety_checklist_1_mileage_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>more_than_20,000_miles</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>More than 20,000 miles</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>van_safety_checklist_4_checklist_item_2_choices</t>
+          <t>van_safety_checklist_1_emergency_exit_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_1_emergency_exit_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_1_maintenance_schedule_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_1_maintenance_schedule_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_2_frequency_of_use_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>often</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Often</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_2_frequency_of_use_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>rarely</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Rarely</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_2_frequency_of_use_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>never</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_2_usage_type_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>to_drive_to_work</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>To drive to work</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_2_usage_type_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>to_drive_to_school</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>To drive to school</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_2_usage_type_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>to_drive_to_store</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>To drive to store</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_2_seatbelts_commute_choices</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_2_seatbelts_commute_choices</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_2_maintenance_commute_choices</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_2_maintenance_commute_choices</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_2_emergency_exit_commute_choices</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_2_emergency_exit_commute_choices</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_2_driving_experience_commute_choices</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>less_than_1_year</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Less than 1 year</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_2_driving_experience_commute_choices</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1-5_years</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1-5 years</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_2_driving_experience_commute_choices</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>more_than_5_years</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>More than 5 years</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_2_mileage_commute_choices</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>less_than_10,000_miles</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Less than 10,000 miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_2_mileage_commute_choices</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>10,000-20,000_miles</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>10,000-20,000 miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_2_mileage_commute_choices</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>more_than_20,000_miles</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>More than 20,000 miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_3_frequency_of_use_choices</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>often</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Often</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_3_frequency_of_use_choices</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>rarely</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Rarely</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_3_frequency_of_use_choices</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>never</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_3_usage_type_choices</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>to_drive_to_school</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>To drive to school</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_3_usage_type_choices</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>to_drive_to_store</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>To drive to store</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_3_usage_type_choices</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>to_drive_to_other_places</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>To drive to other places</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_3_seatbelts_family_choices</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_3_seatbelts_family_choices</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_3_maintenance_family_choices</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_3_maintenance_family_choices</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_3_emergency_exit_family_choices</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_3_emergency_exit_family_choices</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_3_driving_experience_family_choices</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>less_than_1_year</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Less than 1 year</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_3_driving_experience_family_choices</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>1-5_years</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>1-5 years</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_3_driving_experience_family_choices</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>more_than_5_years</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>More than 5 years</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_3_mileage_family_choices</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>less_than_10,000_miles</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Less than 10,000 miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_3_mileage_family_choices</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>10,000-20,000_miles</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>10,000-20,000 miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_3_mileage_family_choices</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>more_than_20,000_miles</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>More than 20,000 miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_4_frequency_of_use_choices</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>often</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Often</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_4_frequency_of_use_choices</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>rarely</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Rarely</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_4_frequency_of_use_choices</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>never</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_4_usage_type_choices</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>to_transport_goods</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>To transport goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_4_usage_type_choices</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>to_transport_people</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>To transport people</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_4_usage_type_choices</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>to_transport_both</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>To transport both</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_4_seatbelts_cargo_choices</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_4_seatbelts_cargo_choices</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_4_maintenance_cargo_choices</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_4_maintenance_cargo_choices</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_4_emergency_exit_cargo_choices</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_4_emergency_exit_cargo_choices</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_4_driving_experience_cargo_choices</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>less_than_1_year</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Less than 1 year</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_4_driving_experience_cargo_choices</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>1-5_years</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>1-5 years</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_4_driving_experience_cargo_choices</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>more_than_5_years</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>More than 5 years</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_4_mileage_cargo_choices</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>less_than_10,000_miles</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Less than 10,000 miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_4_mileage_cargo_choices</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>10,000-20,000_miles</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>10,000-20,000 miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>van_safety_checklist_4_mileage_cargo_choices</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>more_than_20,000_miles</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>More than 20,000 miles</t>
         </is>
       </c>
     </row>
